--- a/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -451,7 +451,7 @@
     <t>166</t>
   </si>
   <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
   </si>
   <si>
     <t>167</t>
@@ -1033,7 +1033,7 @@
     <t>286</t>
   </si>
   <si>
-    <t>Club Equipe de Prévention</t>
+    <t>Service de prévention spécialisée</t>
   </si>
   <si>
     <t>289</t>
@@ -2060,6 +2060,15 @@
   </si>
   <si>
     <t>Les centres de santé et de médiation en santé sexuelle (CSMSS) sont des établissements de santé dérogatoires relevant de l’article L. 6323-1 du code de la santé publique (CSP). Ils ont initialement fait l’objet d’une expérimentation dans le cadre du dispositif prévu à l’article 51 de la loi de financement de la sécurité sociale, au cours de laquelle ils étaient rattachés au numéro FINESS des centres de santé de droit commun. L’activité des centres de santé et de médiation en santé sexuelle (CSMSS) consiste à assurer l’accueil, l’information, la prévention, le dépistage et l’accompagnement des publics dans le domaine de la santé sexuelle dans une approche globale intégrant notamment la prévention et la prise en charge des infections sexuellement transmissibles (IST) et du VIH, la prescription de la contraception et la mise en place de parcours en santé sexuelle.</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
+  </si>
+  <si>
+    <t>Les DSRP ont pour mission principale l’animation régionale des professionnels de la périnatalité et l’accompagnement des évolutions de l’offre et des pratiques, dans un contexte marqué par des enjeux forts en matière de qualité des soins, de prévention, de démographie médicale et d’organisation des parcours. Ils contribuent à la lisibilité et à la cohérence de l’offre de soins périnatals sur les territoires, en favorisant la coordination entre la ville, l’hôpital et les services de protection maternelle et infantile (PMI).</t>
   </si>
   <si>
     <t>690</t>
@@ -2547,7 +2556,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6288,17 +6297,19 @@
       <c r="C311" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="D311" s="2"/>
+      <c r="D311" t="s" s="2">
+        <v>684</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -6307,10 +6318,10 @@
         <v>61</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -6319,10 +6330,10 @@
         <v>61</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -6331,10 +6342,10 @@
         <v>61</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -6343,10 +6354,10 @@
         <v>61</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -6355,14 +6366,12 @@
         <v>61</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="D317" t="s" s="2">
         <v>696</v>
       </c>
+      <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
@@ -6375,7 +6384,7 @@
         <v>698</v>
       </c>
       <c r="D318" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="319">
@@ -6383,13 +6392,13 @@
         <v>61</v>
       </c>
       <c r="B319" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C319" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="D319" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="C319" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="D319" t="s" s="2">
-        <v>696</v>
       </c>
     </row>
     <row r="320">
@@ -6397,25 +6406,39 @@
         <v>61</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="D320" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="D320" t="s" s="2">
+        <v>699</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="D321" t="s" s="2">
         <v>705</v>
+      </c>
+      <c r="D321" s="2"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B322" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C322" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="D322" t="s" s="2">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -118,1060 +118,1060 @@
     <t>Count</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>Date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>Date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Centre Parents-Enfants de moins de 3 ans</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Service de prévention spécialisée</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
     <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>Unité Mobile Hospitalière</t>
@@ -4510,10 +4510,10 @@
         <v>61</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -4522,7 +4522,7 @@
         <v>61</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>385</v>
+        <v>34</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>386</v>
